--- a/log/Table.xlsx
+++ b/log/Table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="224">
   <si>
     <t>Name</t>
   </si>
@@ -23,10 +23,136 @@
     <t>Details</t>
   </si>
   <si>
+    <t>Vivado Commands</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">add_files {{D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/FRegFile.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/mem/DataRam.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ImmGen.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/UartRx.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/WB.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/UartTx.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/FPAdd.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/IF.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ControlUnit.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/mem/InstRam.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/other/ButtonDebounce.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/IO/MMIO.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/DebugController.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/RegFile.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/MEM.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/Decoder.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/EX.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ALU.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ID.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/IO/SevenSeg.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/top/TopDebug.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/BranchUnit.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/CPU.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/VPU.v}}
+</t>
+  </si>
+  <si>
+    <t>filemgmt 56-12</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/mem/DataRam.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ImmGen.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/UartRx.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/WB.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/UartTx.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/IF.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ControlUnit.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/mem/InstRam.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/other/ButtonDebounce.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/IO/MMIO.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/DebugController.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/RegFile.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/MEM.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/Decoder.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/EX.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ALU.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ID.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/IO/SevenSeg.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/top/TopDebug.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/BranchUnit.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/CPU.v' cannot be added to the project because it already exists in the project, skipping this file
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refresh_hw_device -update_hw_probes false [lindex [get_hw_devices xc7a35t_0] 0]
+</t>
+  </si>
+  <si>
+    <t>Labtools 27-3361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The debug hub core was not detected.
+Resolution: 
+1. Make sure the clock connected to the debug hub (dbg_hub) core is a free running clock and is active.
+2. Make sure the BSCAN_SWITCH_USER_MASK device property in Vivado Hardware Manager reflects the user scan chain setting in the design and refresh the device.  To determine the user scan chain setting in the design, open the implemented design and use 'get_property C_USER_SCAN_CHAIN [get_debug_cores dbg_hub]'.
+For more details on setting the scan chain property, consult the Vivado Debug and Programming User Guide (UG908).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refresh_hw_device [lindex [get_hw_devices xc7a35t_0] 0]
+</t>
+  </si>
+  <si>
     <t>Synthesis</t>
   </si>
   <si>
-    <t/>
+    <t>D:\comp sci\CS202 Computer Organization\OrganProj\cpu-project-team\src\top\TopDebug.v</t>
+  </si>
+  <si>
+    <t>Synth 8-992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clk_cpu is already implicitly declared earlier
+</t>
   </si>
   <si>
     <t>D:\comp sci\CS202 Computer Organization\OrganProj\cpu-project-team\src\debug_code\DebugController.v</t>
@@ -35,9 +161,6 @@
     <t>Synth 8-5788</t>
   </si>
   <si>
-    <t>Warning</t>
-  </si>
-  <si>
     <t xml:space="preserve">Register payload_reg[0] in module DebugController is has both Set and reset with same priority. This may cause simulation mismatches. Consider rewriting code 
 </t>
   </si>
@@ -97,78 +220,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[31]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[30]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[29]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[28]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[27]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[26]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[25]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[24]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[23]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[22]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[21]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[20]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[19]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[18]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[17]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[16]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[15]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr[14]
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">design DatatRam has unconnected port addr[1]
 </t>
   </si>
@@ -177,78 +228,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[31]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[30]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[29]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[28]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[27]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[26]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[25]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[24]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[23]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[22]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[21]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[20]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[19]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[18]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[17]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[16]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[15]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design DatatRam has unconnected port addr_b[14]
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">design DatatRam has unconnected port addr_b[1]
 </t>
   </si>
@@ -405,70 +384,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[31]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[30]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[29]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[28]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[27]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[26]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[25]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[24]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[23]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[22]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[21]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[20]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[19]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[18]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[17]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">design Accelerator has unconnected port rs1_data[16]
-</t>
-  </si>
-  <si>
     <t>D:\comp sci\CS202 Computer Organization\OrganProj\cpu-project-team\src\IO\SevenSeg.v</t>
   </si>
   <si>
@@ -479,13 +394,6 @@
 </t>
   </si>
   <si>
-    <t>Synth 8-3463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infeasible ramstyle = block set for RAM u_data_ram/mem_reg,trying to implement using LUTRAM
-</t>
-  </si>
-  <si>
     <t>Synth 8-3332</t>
   </si>
   <si>
@@ -848,31 +756,121 @@
     <t>Implementation</t>
   </si>
   <si>
-    <t>Route Design</t>
-  </si>
-  <si>
-    <t>Route 35-328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Router estimated timing not met.
-Resolution: For a complete and accurate timing signoff, report_timing_summary must be run after route_design. Alternatively, route_design can be run with the -timing_summary option to enable a complete timing signoff at the end of route_design.
-</t>
-  </si>
-  <si>
-    <t>Timing 38-282</t>
-  </si>
-  <si>
-    <t>Critical Warning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The design failed to meet the timing requirements. Please see the timing summary report for details on the timing violations.
+    <t>Place Design</t>
+  </si>
+  <si>
+    <t>DRC</t>
+  </si>
+  <si>
+    <t>DRC System</t>
+  </si>
+  <si>
+    <t>Rule limit reached</t>
+  </si>
+  <si>
+    <t>DRC CHECK-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report rule limit reached: REQP-1839 rule limit reached: 20 violations have been found.
+</t>
+  </si>
+  <si>
+    <t>Netlist</t>
+  </si>
+  <si>
+    <t>Instance</t>
+  </si>
+  <si>
+    <t>Required Pin</t>
+  </si>
+  <si>
+    <t>RAMB36E1</t>
+  </si>
+  <si>
+    <t>DRC REQP-1839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[10] (net: u_data_ram/Q[7]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[9]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[11] (net: u_data_ram/Q[8]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[10]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[12] (net: u_data_ram/Q[9]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[11]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[13] (net: u_data_ram/Q[10]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[12]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[14] (net: u_data_ram/Q[11]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[13]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[3] (net: u_data_ram/Q[0]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[2]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[4] (net: u_data_ram/Q[1]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[3]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[5] (net: u_data_ram/Q[2]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[4]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[6] (net: u_data_ram/Q[3]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[5]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[7] (net: u_data_ram/Q[4]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[6]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[8] (net: u_data_ram/Q[5]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[7]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[9] (net: u_data_ram/Q[6]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[8]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][3]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][4]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][6]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][7]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][8]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][9]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[1][7]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[1][8]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
 </t>
   </si>
   <si>
     <t>Write Bitstream</t>
-  </si>
-  <si>
-    <t>DRC</t>
   </si>
   <si>
     <t>Pin Planning</t>
@@ -933,7 +931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
       <alignment horizontal="general" vertical="top"/>
@@ -953,6 +951,18 @@
     <xf numFmtId="18" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="general" vertical="top" indent="4"/>
     </xf>
+    <xf numFmtId="18" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="general" vertical="top" indent="5"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="general" vertical="top" indent="6"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="general" vertical="top" indent="7"/>
+    </xf>
+    <xf numFmtId="18" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="general" vertical="top" indent="8"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -963,7 +973,7 @@
     <outlinePr summaryBelow="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" outlineLevelRow="4"/>
+  <sheetFormatPr defaultRowHeight="15.0" outlineLevelRow="8"/>
   <cols>
     <col min="1" max="1" width="11.71875" customWidth="true"/>
     <col min="2" max="2" width="11.71875" customWidth="true"/>
@@ -1014,8 +1024,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" outlineLevel="2">
-      <c r="A5" t="s" s="4">
+    <row r="5" outlineLevel="3">
+      <c r="A5" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B5" t="s" s="2">
@@ -1025,8 +1035,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" outlineLevel="2">
-      <c r="A6" t="s" s="4">
+    <row r="6" outlineLevel="3">
+      <c r="A6" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B6" t="s" s="2">
@@ -1036,8 +1046,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" outlineLevel="2">
-      <c r="A7" t="s" s="4">
+    <row r="7" outlineLevel="3">
+      <c r="A7" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B7" t="s" s="2">
@@ -1047,8 +1057,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" outlineLevel="2">
-      <c r="A8" t="s" s="4">
+    <row r="8" outlineLevel="3">
+      <c r="A8" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B8" t="s" s="2">
@@ -1058,8 +1068,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" outlineLevel="2">
-      <c r="A9" t="s" s="4">
+    <row r="9" outlineLevel="3">
+      <c r="A9" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B9" t="s" s="2">
@@ -1069,8 +1079,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" outlineLevel="2">
-      <c r="A10" t="s" s="4">
+    <row r="10" outlineLevel="3">
+      <c r="A10" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B10" t="s" s="2">
@@ -1080,8 +1090,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" outlineLevel="2">
-      <c r="A11" t="s" s="4">
+    <row r="11" outlineLevel="3">
+      <c r="A11" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B11" t="s" s="2">
@@ -1091,8 +1101,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" outlineLevel="2">
-      <c r="A12" t="s" s="4">
+    <row r="12" outlineLevel="3">
+      <c r="A12" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B12" t="s" s="2">
@@ -1102,8 +1112,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" outlineLevel="2">
-      <c r="A13" t="s" s="4">
+    <row r="13" outlineLevel="3">
+      <c r="A13" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B13" t="s" s="2">
@@ -1113,8 +1123,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" outlineLevel="2">
-      <c r="A14" t="s" s="4">
+    <row r="14" outlineLevel="3">
+      <c r="A14" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B14" t="s" s="2">
@@ -1124,8 +1134,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" outlineLevel="2">
-      <c r="A15" t="s" s="4">
+    <row r="15" outlineLevel="3">
+      <c r="A15" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B15" t="s" s="2">
@@ -1135,8 +1145,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" outlineLevel="2">
-      <c r="A16" t="s" s="4">
+    <row r="16" outlineLevel="3">
+      <c r="A16" t="s" s="5">
         <v>6</v>
       </c>
       <c r="B16" t="s" s="2">
@@ -1146,108 +1156,108 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" outlineLevel="1">
-      <c r="A17" t="s" s="3">
+    <row r="17" outlineLevel="3">
+      <c r="A17" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B17" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s" s="2">
+    </row>
+    <row r="18" outlineLevel="3">
+      <c r="A18" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="18" outlineLevel="2">
-      <c r="A18" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C18" t="s" s="2">
+    <row r="19" outlineLevel="3">
+      <c r="A19" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="19" outlineLevel="2">
-      <c r="A19" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C19" t="s" s="2">
+    <row r="20" outlineLevel="3">
+      <c r="A20" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="20" outlineLevel="2">
-      <c r="A20" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s" s="2">
+    <row r="21" outlineLevel="3">
+      <c r="A21" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="21" outlineLevel="2">
-      <c r="A21" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C21" t="s" s="2">
+    <row r="22" outlineLevel="3">
+      <c r="A22" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>26</v>
       </c>
     </row>
-    <row r="22" outlineLevel="2">
-      <c r="A22" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C22" t="s" s="2">
+    <row r="23" outlineLevel="3">
+      <c r="A23" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>27</v>
       </c>
     </row>
-    <row r="23" outlineLevel="2">
-      <c r="A23" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C23" t="s" s="2">
+    <row r="24" outlineLevel="3">
+      <c r="A24" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="24" outlineLevel="2">
-      <c r="A24" t="s" s="4">
-        <v>21</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C24" t="s" s="2">
+    <row r="25" outlineLevel="1">
+      <c r="A25" t="s" s="3">
         <v>29</v>
       </c>
-    </row>
-    <row r="25" outlineLevel="2">
-      <c r="A25" t="s" s="4">
-        <v>21</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" outlineLevel="2">
       <c r="A26" t="s" s="4">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>7</v>
@@ -1256,53 +1266,53 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" outlineLevel="2">
-      <c r="A27" t="s" s="4">
-        <v>21</v>
+    <row r="27" outlineLevel="1">
+      <c r="A27" t="s" s="3">
+        <v>32</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" outlineLevel="2">
       <c r="A28" t="s" s="4">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C28" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
         <v>33</v>
       </c>
-    </row>
-    <row r="29" outlineLevel="2">
-      <c r="A29" t="s" s="4">
-        <v>21</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C29" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1">
+      <c r="A30" t="s" s="3">
         <v>34</v>
       </c>
-    </row>
-    <row r="30" outlineLevel="2">
-      <c r="A30" t="s" s="4">
-        <v>21</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" outlineLevel="2">
       <c r="A31" t="s" s="4">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>7</v>
@@ -1311,2105 +1321,2358 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" outlineLevel="2">
-      <c r="A32" t="s" s="4">
-        <v>21</v>
+    <row r="32" outlineLevel="1">
+      <c r="A32" t="s" s="3">
+        <v>37</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>37</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" outlineLevel="2">
       <c r="A33" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" outlineLevel="2">
       <c r="A34" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" outlineLevel="2">
       <c r="A35" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" outlineLevel="2">
       <c r="A36" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" outlineLevel="2">
       <c r="A37" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" outlineLevel="2">
       <c r="A38" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" outlineLevel="2">
       <c r="A39" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" outlineLevel="2">
       <c r="A40" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" outlineLevel="2">
       <c r="A41" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" outlineLevel="2">
       <c r="A42" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" outlineLevel="2">
       <c r="A43" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" outlineLevel="2">
       <c r="A44" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" outlineLevel="2">
       <c r="A45" t="s" s="4">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" outlineLevel="2">
-      <c r="A46" t="s" s="4">
-        <v>21</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1">
+      <c r="A46" t="s" s="3">
+        <v>52</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" outlineLevel="2">
       <c r="A47" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" outlineLevel="2">
       <c r="A48" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" outlineLevel="2">
       <c r="A49" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" outlineLevel="2">
       <c r="A50" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" outlineLevel="2">
       <c r="A51" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" outlineLevel="2">
       <c r="A52" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" outlineLevel="2">
       <c r="A53" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="54" outlineLevel="2">
       <c r="A54" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" outlineLevel="2">
       <c r="A55" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" outlineLevel="2">
       <c r="A56" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" outlineLevel="2">
       <c r="A57" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" outlineLevel="2">
       <c r="A58" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" outlineLevel="2">
       <c r="A59" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" outlineLevel="2">
       <c r="A60" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" outlineLevel="2">
       <c r="A61" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" outlineLevel="2">
       <c r="A62" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" outlineLevel="2">
       <c r="A63" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" outlineLevel="2">
       <c r="A64" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65" outlineLevel="2">
       <c r="A65" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" outlineLevel="2">
       <c r="A66" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67" outlineLevel="2">
       <c r="A67" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68" outlineLevel="2">
       <c r="A68" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" outlineLevel="2">
       <c r="A69" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" outlineLevel="2">
       <c r="A70" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="71" outlineLevel="2">
       <c r="A71" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" outlineLevel="2">
       <c r="A72" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" outlineLevel="2">
       <c r="A73" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" outlineLevel="2">
       <c r="A74" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" outlineLevel="2">
       <c r="A75" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" outlineLevel="2">
       <c r="A76" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77" outlineLevel="2">
       <c r="A77" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" outlineLevel="2">
       <c r="A78" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" outlineLevel="2">
       <c r="A79" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="80" outlineLevel="2">
       <c r="A80" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" outlineLevel="2">
       <c r="A81" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="82" outlineLevel="2">
       <c r="A82" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="83" outlineLevel="2">
       <c r="A83" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84" outlineLevel="2">
       <c r="A84" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" outlineLevel="2">
       <c r="A85" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" outlineLevel="2">
       <c r="A86" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="87" outlineLevel="2">
       <c r="A87" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" outlineLevel="2">
       <c r="A88" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>93</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89" outlineLevel="2">
       <c r="A89" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>94</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90" outlineLevel="2">
       <c r="A90" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>95</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" outlineLevel="2">
       <c r="A91" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>96</v>
+        <v>56</v>
       </c>
     </row>
     <row r="92" outlineLevel="2">
       <c r="A92" t="s" s="4">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="93" outlineLevel="2">
-      <c r="A93" t="s" s="4">
-        <v>21</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" outlineLevel="1">
+      <c r="A93" t="s" s="3">
+        <v>95</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>98</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" outlineLevel="2">
       <c r="A94" t="s" s="4">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" outlineLevel="2">
       <c r="A95" t="s" s="4">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" outlineLevel="2">
-      <c r="A96" t="s" s="4">
-        <v>21</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" outlineLevel="1">
+      <c r="A96" t="s" s="3">
+        <v>98</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" outlineLevel="2">
       <c r="A97" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98" outlineLevel="2">
       <c r="A98" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" outlineLevel="2">
       <c r="A99" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="100" outlineLevel="2">
       <c r="A100" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" outlineLevel="2">
       <c r="A101" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="102" outlineLevel="2">
       <c r="A102" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" outlineLevel="2">
       <c r="A103" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" outlineLevel="2">
       <c r="A104" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105" outlineLevel="2">
       <c r="A105" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="106" outlineLevel="2">
       <c r="A106" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="107" outlineLevel="2">
       <c r="A107" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="108" outlineLevel="2">
       <c r="A108" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="109" outlineLevel="2">
       <c r="A109" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="110" outlineLevel="2">
       <c r="A110" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="111" outlineLevel="2">
       <c r="A111" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>22</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" outlineLevel="2">
       <c r="A112" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>23</v>
+        <v>115</v>
       </c>
     </row>
     <row r="113" outlineLevel="2">
       <c r="A113" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>24</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" outlineLevel="2">
       <c r="A114" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>25</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" outlineLevel="2">
       <c r="A115" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>26</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" outlineLevel="2">
       <c r="A116" t="s" s="4">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="117" outlineLevel="1">
-      <c r="A117" t="s" s="3">
-        <v>116</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="117" outlineLevel="2">
+      <c r="A117" t="s" s="4">
+        <v>98</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>4</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" outlineLevel="2">
       <c r="A118" t="s" s="4">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" outlineLevel="2">
       <c r="A119" t="s" s="4">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" outlineLevel="1">
-      <c r="A120" t="s" s="3">
-        <v>119</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="120" outlineLevel="2">
+      <c r="A120" t="s" s="4">
+        <v>98</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="121" outlineLevel="2">
       <c r="A121" t="s" s="4">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="122" outlineLevel="2">
       <c r="A122" t="s" s="4">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="123" outlineLevel="2">
       <c r="A123" t="s" s="4">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" outlineLevel="2">
       <c r="A124" t="s" s="4">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="125" outlineLevel="2">
       <c r="A125" t="s" s="4">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="126" outlineLevel="1">
-      <c r="A126" t="s" s="3">
-        <v>121</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="126" outlineLevel="2">
+      <c r="A126" t="s" s="4">
+        <v>98</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="127" outlineLevel="2">
       <c r="A127" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="128" outlineLevel="2">
       <c r="A128" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="129" outlineLevel="2">
       <c r="A129" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="130" outlineLevel="2">
       <c r="A130" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="131" outlineLevel="2">
       <c r="A131" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="132" outlineLevel="2">
       <c r="A132" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="133" outlineLevel="2">
       <c r="A133" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="134" outlineLevel="2">
       <c r="A134" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" outlineLevel="2">
       <c r="A135" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="136" outlineLevel="2">
       <c r="A136" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="137" outlineLevel="2">
       <c r="A137" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="138" outlineLevel="2">
       <c r="A138" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="139" outlineLevel="2">
       <c r="A139" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="140" outlineLevel="2">
       <c r="A140" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="141" outlineLevel="2">
       <c r="A141" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="142" outlineLevel="2">
       <c r="A142" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="143" outlineLevel="2">
       <c r="A143" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" outlineLevel="2">
       <c r="A144" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="145" outlineLevel="2">
       <c r="A145" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="146" outlineLevel="2">
       <c r="A146" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="147" outlineLevel="2">
       <c r="A147" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="148" outlineLevel="2">
       <c r="A148" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="149" outlineLevel="2">
       <c r="A149" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="150" outlineLevel="2">
       <c r="A150" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="151" outlineLevel="2">
       <c r="A151" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="152" outlineLevel="2">
       <c r="A152" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="153" outlineLevel="2">
       <c r="A153" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="154" outlineLevel="2">
       <c r="A154" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="155" outlineLevel="2">
       <c r="A155" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="156" outlineLevel="2">
       <c r="A156" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="157" outlineLevel="2">
       <c r="A157" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="158" outlineLevel="2">
       <c r="A158" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="159" outlineLevel="2">
       <c r="A159" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="160" outlineLevel="2">
       <c r="A160" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="161" outlineLevel="2">
       <c r="A161" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="162" outlineLevel="2">
       <c r="A162" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" outlineLevel="2">
       <c r="A163" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="164" outlineLevel="2">
       <c r="A164" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="165" outlineLevel="2">
       <c r="A165" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" outlineLevel="2">
       <c r="A166" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="167" outlineLevel="2">
       <c r="A167" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168" outlineLevel="2">
       <c r="A168" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="169" outlineLevel="2">
       <c r="A169" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="170" outlineLevel="2">
       <c r="A170" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="171" outlineLevel="2">
       <c r="A171" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" outlineLevel="2">
       <c r="A172" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="173" outlineLevel="2">
       <c r="A173" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="174" outlineLevel="2">
       <c r="A174" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="175" outlineLevel="2">
       <c r="A175" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="176" outlineLevel="2">
       <c r="A176" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="177" outlineLevel="2">
       <c r="A177" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="178" outlineLevel="2">
       <c r="A178" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="179" outlineLevel="2">
       <c r="A179" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" outlineLevel="2">
       <c r="A180" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
     <row r="181" outlineLevel="2">
       <c r="A181" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="182" outlineLevel="2">
       <c r="A182" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="183" outlineLevel="2">
       <c r="A183" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184" outlineLevel="2">
       <c r="A184" t="s" s="4">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="185" outlineLevel="2">
-      <c r="A185" t="s" s="4">
-        <v>121</v>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>188</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="186" outlineLevel="2">
-      <c r="A186" t="s" s="4">
-        <v>121</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" outlineLevel="1">
+      <c r="A186" t="s" s="3">
+        <v>189</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>182</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187" outlineLevel="2">
       <c r="A187" t="s" s="4">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="188" outlineLevel="2">
-      <c r="A188" t="s" s="4">
-        <v>121</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" outlineLevel="3">
+      <c r="A188" t="s" s="5">
+        <v>191</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="189" outlineLevel="2">
-      <c r="A189" t="s" s="4">
-        <v>121</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" outlineLevel="4">
+      <c r="A189" t="s" s="6">
+        <v>192</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="190" outlineLevel="2">
-      <c r="A190" t="s" s="4">
-        <v>121</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" outlineLevel="5">
+      <c r="A190" t="s" s="7">
+        <v>193</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="191" outlineLevel="2">
-      <c r="A191" t="s" s="4">
-        <v>121</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="191" outlineLevel="3">
+      <c r="A191" t="s" s="5">
+        <v>195</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="192" outlineLevel="2">
-      <c r="A192" t="s" s="4">
-        <v>121</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" outlineLevel="4">
+      <c r="A192" t="s" s="6">
+        <v>196</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="193" outlineLevel="2">
-      <c r="A193" t="s" s="4">
-        <v>121</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" outlineLevel="5">
+      <c r="A193" t="s" s="7">
+        <v>197</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="194" outlineLevel="2">
-      <c r="A194" t="s" s="4">
-        <v>121</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" outlineLevel="6">
+      <c r="A194" t="s" s="8">
+        <v>198</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C194" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" outlineLevel="7">
+      <c r="A195" t="s" s="9">
+        <v>199</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="196" outlineLevel="8">
+      <c r="A196" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C196" t="s" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="197" outlineLevel="8">
+      <c r="A197" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C197" t="s" s="2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="198" outlineLevel="8">
+      <c r="A198" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="199" outlineLevel="8">
+      <c r="A199" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="200" outlineLevel="8">
+      <c r="A200" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C200" t="s" s="2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="201" outlineLevel="8">
+      <c r="A201" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C201" t="s" s="2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="202" outlineLevel="8">
+      <c r="A202" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C202" t="s" s="2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="203" outlineLevel="8">
+      <c r="A203" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C203" t="s" s="2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="204" outlineLevel="8">
+      <c r="A204" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C204" t="s" s="2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="205" outlineLevel="8">
+      <c r="A205" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="206" outlineLevel="8">
+      <c r="A206" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C206" t="s" s="2">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="207" outlineLevel="8">
+      <c r="A207" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C207" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="208" outlineLevel="8">
+      <c r="A208" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C208" t="s" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="209" outlineLevel="8">
+      <c r="A209" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C209" t="s" s="2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="210" outlineLevel="8">
+      <c r="A210" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C210" t="s" s="2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="211" outlineLevel="8">
+      <c r="A211" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C211" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="212" outlineLevel="8">
+      <c r="A212" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C212" t="s" s="2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="213" outlineLevel="8">
+      <c r="A213" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C213" t="s" s="2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="214" outlineLevel="8">
+      <c r="A214" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C214" t="s" s="2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="215" outlineLevel="1">
+      <c r="A215" t="s" s="3">
+        <v>220</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C215" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" outlineLevel="2">
+      <c r="A216" t="s" s="4">
         <v>190</v>
       </c>
-    </row>
-    <row r="195" outlineLevel="2">
-      <c r="A195" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C195" t="s" s="2">
+      <c r="B216" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C216" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" outlineLevel="3">
+      <c r="A217" t="s" s="5">
+        <v>221</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C217" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" outlineLevel="4">
+      <c r="A218" t="s" s="6">
+        <v>222</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C218" t="s" s="2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="219" outlineLevel="3">
+      <c r="A219" t="s" s="5">
         <v>191</v>
       </c>
-    </row>
-    <row r="196" outlineLevel="2">
-      <c r="A196" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C196" t="s" s="2">
+      <c r="B219" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C219" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" outlineLevel="4">
+      <c r="A220" t="s" s="6">
         <v>192</v>
       </c>
-    </row>
-    <row r="197" outlineLevel="2">
-      <c r="A197" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C197" t="s" s="2">
+      <c r="B220" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C220" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" outlineLevel="5">
+      <c r="A221" t="s" s="7">
         <v>193</v>
       </c>
-    </row>
-    <row r="198" outlineLevel="2">
-      <c r="A198" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C198" t="s" s="2">
+      <c r="B221" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C221" t="s" s="2">
         <v>194</v>
       </c>
     </row>
-    <row r="199" outlineLevel="2">
-      <c r="A199" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C199" t="s" s="2">
+    <row r="222" outlineLevel="3">
+      <c r="A222" t="s" s="5">
         <v>195</v>
       </c>
-    </row>
-    <row r="200" outlineLevel="2">
-      <c r="A200" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C200" t="s" s="2">
+      <c r="B222" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C222" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" outlineLevel="4">
+      <c r="A223" t="s" s="6">
         <v>196</v>
       </c>
-    </row>
-    <row r="201" outlineLevel="2">
-      <c r="A201" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C201" t="s" s="2">
+      <c r="B223" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C223" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" outlineLevel="5">
+      <c r="A224" t="s" s="7">
         <v>197</v>
       </c>
-    </row>
-    <row r="202" outlineLevel="2">
-      <c r="A202" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C202" t="s" s="2">
+      <c r="B224" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C224" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" outlineLevel="6">
+      <c r="A225" t="s" s="8">
         <v>198</v>
       </c>
-    </row>
-    <row r="203" outlineLevel="2">
-      <c r="A203" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C203" t="s" s="2">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="204" outlineLevel="2">
-      <c r="A204" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B204" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C204" t="s" s="2">
+      <c r="B225" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C225" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" outlineLevel="7">
+      <c r="A226" t="s" s="9">
+        <v>199</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C226" t="s" s="2">
         <v>200</v>
       </c>
     </row>
-    <row r="205" outlineLevel="2">
-      <c r="A205" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C205" t="s" s="2">
+    <row r="227" outlineLevel="8">
+      <c r="A227" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C227" t="s" s="2">
         <v>201</v>
       </c>
     </row>
-    <row r="206" outlineLevel="2">
-      <c r="A206" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B206" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C206" t="s" s="2">
+    <row r="228" outlineLevel="8">
+      <c r="A228" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C228" t="s" s="2">
         <v>202</v>
       </c>
     </row>
-    <row r="207" outlineLevel="2">
-      <c r="A207" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C207" t="s" s="2">
+    <row r="229" outlineLevel="8">
+      <c r="A229" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C229" t="s" s="2">
         <v>203</v>
       </c>
     </row>
-    <row r="208" outlineLevel="2">
-      <c r="A208" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B208" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C208" t="s" s="2">
+    <row r="230" outlineLevel="8">
+      <c r="A230" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C230" t="s" s="2">
         <v>204</v>
       </c>
     </row>
-    <row r="209" outlineLevel="2">
-      <c r="A209" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B209" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C209" t="s" s="2">
+    <row r="231" outlineLevel="8">
+      <c r="A231" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C231" t="s" s="2">
         <v>205</v>
       </c>
     </row>
-    <row r="210" outlineLevel="2">
-      <c r="A210" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B210" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C210" t="s" s="2">
+    <row r="232" outlineLevel="8">
+      <c r="A232" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C232" t="s" s="2">
         <v>206</v>
       </c>
     </row>
-    <row r="211" outlineLevel="2">
-      <c r="A211" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B211" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C211" t="s" s="2">
+    <row r="233" outlineLevel="8">
+      <c r="A233" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C233" t="s" s="2">
         <v>207</v>
       </c>
     </row>
-    <row r="212" outlineLevel="2">
-      <c r="A212" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C212" t="s" s="2">
+    <row r="234" outlineLevel="8">
+      <c r="A234" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C234" t="s" s="2">
         <v>208</v>
       </c>
     </row>
-    <row r="213" outlineLevel="2">
-      <c r="A213" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B213" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C213" t="s" s="2">
+    <row r="235" outlineLevel="8">
+      <c r="A235" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C235" t="s" s="2">
         <v>209</v>
       </c>
     </row>
-    <row r="214" outlineLevel="2">
-      <c r="A214" t="s" s="4">
-        <v>121</v>
-      </c>
-      <c r="B214" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C214" t="s" s="2">
+    <row r="236" outlineLevel="8">
+      <c r="A236" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C236" t="s" s="2">
         <v>210</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="s" s="2">
+    <row r="237" outlineLevel="8">
+      <c r="A237" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C237" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="B215" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" outlineLevel="1">
-      <c r="A216" t="s" s="3">
+    </row>
+    <row r="238" outlineLevel="8">
+      <c r="A238" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C238" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="B216" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C216" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" outlineLevel="2">
-      <c r="A217" t="s" s="4">
+    </row>
+    <row r="239" outlineLevel="8">
+      <c r="A239" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C239" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="B217" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C217" t="s" s="2">
+    </row>
+    <row r="240" outlineLevel="8">
+      <c r="A240" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C240" t="s" s="2">
         <v>214</v>
       </c>
     </row>
-    <row r="218" outlineLevel="2">
-      <c r="A218" t="s" s="4">
+    <row r="241" outlineLevel="8">
+      <c r="A241" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C241" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="B218" t="s" s="2">
+    </row>
+    <row r="242" outlineLevel="8">
+      <c r="A242" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C242" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="C218" t="s" s="2">
+    </row>
+    <row r="243" outlineLevel="8">
+      <c r="A243" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C243" t="s" s="2">
         <v>217</v>
       </c>
     </row>
-    <row r="219" outlineLevel="1">
-      <c r="A219" t="s" s="3">
+    <row r="244" outlineLevel="8">
+      <c r="A244" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C244" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="B219" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C219" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="220" outlineLevel="2">
-      <c r="A220" t="s" s="4">
+    </row>
+    <row r="245" outlineLevel="8">
+      <c r="A245" t="s" s="10">
+        <v>199</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C245" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C220" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" outlineLevel="3">
-      <c r="A221" t="s" s="5">
-        <v>220</v>
-      </c>
-      <c r="B221" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C221" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" outlineLevel="4">
-      <c r="A222" t="s" s="6">
-        <v>221</v>
-      </c>
-      <c r="B222" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C222" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/log/Table.xlsx
+++ b/log/Table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="180">
   <si>
     <t>Name</t>
   </si>
@@ -23,144 +23,21 @@
     <t>Details</t>
   </si>
   <si>
-    <t>Vivado Commands</t>
+    <t>Synthesis</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t xml:space="preserve">add_files {{D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/FRegFile.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/mem/DataRam.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ImmGen.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/UartRx.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/WB.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/UartTx.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/FPAdd.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/IF.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ControlUnit.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/mem/InstRam.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/other/ButtonDebounce.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/IO/MMIO.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/DebugController.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/RegFile.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/MEM.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/Decoder.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/EX.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ALU.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ID.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/IO/SevenSeg.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/top/TopDebug.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/BranchUnit.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/CPU.v} {D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/VPU.v}}
-</t>
-  </si>
-  <si>
-    <t>filemgmt 56-12</t>
+    <t>D:\comp_sci\CS202 Computer Organization\OrganProj\cpu-project-team\src\debug_code\DebugController.v</t>
+  </si>
+  <si>
+    <t>Synth 8-5788</t>
   </si>
   <si>
     <t>Warning</t>
   </si>
   <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/mem/DataRam.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ImmGen.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/UartRx.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/WB.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/UartTx.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/IF.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ControlUnit.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/mem/InstRam.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/other/ButtonDebounce.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/IO/MMIO.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/debug_code/DebugController.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/RegFile.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/MEM.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/Decoder.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/EX.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ALU.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/ID.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/IO/SevenSeg.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/top/TopDebug.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/BranchUnit.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File 'D:/comp sci/CS202 Computer Organization/OrganProj/cpu-project-team/src/core/CPU.v' cannot be added to the project because it already exists in the project, skipping this file
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refresh_hw_device -update_hw_probes false [lindex [get_hw_devices xc7a35t_0] 0]
-</t>
-  </si>
-  <si>
-    <t>Labtools 27-3361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The debug hub core was not detected.
-Resolution: 
-1. Make sure the clock connected to the debug hub (dbg_hub) core is a free running clock and is active.
-2. Make sure the BSCAN_SWITCH_USER_MASK device property in Vivado Hardware Manager reflects the user scan chain setting in the design and refresh the device.  To determine the user scan chain setting in the design, open the implemented design and use 'get_property C_USER_SCAN_CHAIN [get_debug_cores dbg_hub]'.
-For more details on setting the scan chain property, consult the Vivado Debug and Programming User Guide (UG908).
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">refresh_hw_device [lindex [get_hw_devices xc7a35t_0] 0]
-</t>
-  </si>
-  <si>
-    <t>Synthesis</t>
-  </si>
-  <si>
-    <t>D:\comp sci\CS202 Computer Organization\OrganProj\cpu-project-team\src\top\TopDebug.v</t>
-  </si>
-  <si>
-    <t>Synth 8-992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clk_cpu is already implicitly declared earlier
-</t>
-  </si>
-  <si>
-    <t>D:\comp sci\CS202 Computer Organization\OrganProj\cpu-project-team\src\debug_code\DebugController.v</t>
-  </si>
-  <si>
-    <t>Synth 8-5788</t>
-  </si>
-  <si>
     <t xml:space="preserve">Register payload_reg[0] in module DebugController is has both Set and reset with same priority. This may cause simulation mismatches. Consider rewriting code 
 </t>
   </si>
@@ -384,7 +261,7 @@
 </t>
   </si>
   <si>
-    <t>D:\comp sci\CS202 Computer Organization\OrganProj\cpu-project-team\src\IO\SevenSeg.v</t>
+    <t>D:\comp_sci\CS202 Computer Organization\OrganProj\cpu-project-team\src\IO\SevenSeg.v</t>
   </si>
   <si>
     <t>Synth 8-6014</t>
@@ -756,6 +633,16 @@
     <t>Implementation</t>
   </si>
   <si>
+    <t>Opt Design</t>
+  </si>
+  <si>
+    <t>Pwropt 34-321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HACOOException: Too many TFIs and TFOs in design, exiting pwropt. You can change this limit with the param pwropt.maxFaninFanoutToNetRatio
+</t>
+  </si>
+  <si>
     <t>Place Design</t>
   </si>
   <si>
@@ -794,79 +681,14 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[11] (net: u_data_ram/Q[8]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[10]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[12] (net: u_data_ram/Q[9]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[11]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[13] (net: u_data_ram/Q[10]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[12]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[14] (net: u_data_ram/Q[11]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[13]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[3] (net: u_data_ram/Q[0]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[2]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[4] (net: u_data_ram/Q[1]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[3]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[5] (net: u_data_ram/Q[2]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[4]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[6] (net: u_data_ram/Q[3]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[5]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[7] (net: u_data_ram/Q[4]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[6]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[8] (net: u_data_ram/Q[5]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[7]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRARDADDR[9] (net: u_data_ram/Q[6]) which is driven by a register (u_debug_ctrl/dmem_dbg_addr_reg[8]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][3]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][4]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][6]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][7]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][8]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[17][9]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[1][7]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMB36 async control check: The RAMB36E1 u_data_ram/mem_reg_0 has an input control pin u_data_ram/mem_reg_0/ADDRBWRADDR[14] (net: u_data_ram/load_addr_r_reg[29][12]) which is driven by a register (u_cpu/u_id/u_reg_file/regs_reg[1][8]) that has an active asychronous set or reset. This may cause corruption of the memory contents and/or read values when the set/reset is asserted and is not analyzed by the default static timing analysis. It is suggested to eliminate the use of a set/reset to registers driving this RAMB pin or else use a synchronous reset in which the assertion of the reset is timed by default.
+    <t>Route Design</t>
+  </si>
+  <si>
+    <t>Route 35-328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Router estimated timing not met.
+Resolution: For a complete and accurate timing signoff, report_timing_summary must be run after route_design. Alternatively, route_design can be run with the -timing_summary option to enable a complete timing signoff at the end of route_design.
 </t>
   </si>
   <si>
@@ -931,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
       <alignment horizontal="general" vertical="top"/>
@@ -960,9 +782,6 @@
     <xf numFmtId="18" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="general" vertical="top" indent="7"/>
     </xf>
-    <xf numFmtId="18" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="general" vertical="top" indent="8"/>
-    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -973,7 +792,7 @@
     <outlinePr summaryBelow="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" outlineLevelRow="8"/>
+  <sheetFormatPr defaultRowHeight="15.0" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="11.71875" customWidth="true"/>
     <col min="2" max="2" width="11.71875" customWidth="true"/>
@@ -1024,8 +843,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" outlineLevel="3">
-      <c r="A5" t="s" s="5">
+    <row r="5" outlineLevel="2">
+      <c r="A5" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B5" t="s" s="2">
@@ -1035,8 +854,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" outlineLevel="3">
-      <c r="A6" t="s" s="5">
+    <row r="6" outlineLevel="2">
+      <c r="A6" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B6" t="s" s="2">
@@ -1046,8 +865,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" outlineLevel="3">
-      <c r="A7" t="s" s="5">
+    <row r="7" outlineLevel="2">
+      <c r="A7" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B7" t="s" s="2">
@@ -1057,8 +876,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" outlineLevel="3">
-      <c r="A8" t="s" s="5">
+    <row r="8" outlineLevel="2">
+      <c r="A8" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B8" t="s" s="2">
@@ -1068,8 +887,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" outlineLevel="3">
-      <c r="A9" t="s" s="5">
+    <row r="9" outlineLevel="2">
+      <c r="A9" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B9" t="s" s="2">
@@ -1079,8 +898,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" outlineLevel="3">
-      <c r="A10" t="s" s="5">
+    <row r="10" outlineLevel="2">
+      <c r="A10" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B10" t="s" s="2">
@@ -1090,8 +909,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" outlineLevel="3">
-      <c r="A11" t="s" s="5">
+    <row r="11" outlineLevel="2">
+      <c r="A11" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B11" t="s" s="2">
@@ -1101,8 +920,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" outlineLevel="3">
-      <c r="A12" t="s" s="5">
+    <row r="12" outlineLevel="2">
+      <c r="A12" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B12" t="s" s="2">
@@ -1112,8 +931,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" outlineLevel="3">
-      <c r="A13" t="s" s="5">
+    <row r="13" outlineLevel="2">
+      <c r="A13" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B13" t="s" s="2">
@@ -1123,8 +942,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" outlineLevel="3">
-      <c r="A14" t="s" s="5">
+    <row r="14" outlineLevel="2">
+      <c r="A14" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B14" t="s" s="2">
@@ -1134,8 +953,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" outlineLevel="3">
-      <c r="A15" t="s" s="5">
+    <row r="15" outlineLevel="2">
+      <c r="A15" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B15" t="s" s="2">
@@ -1145,8 +964,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" outlineLevel="3">
-      <c r="A16" t="s" s="5">
+    <row r="16" outlineLevel="2">
+      <c r="A16" t="s" s="4">
         <v>6</v>
       </c>
       <c r="B16" t="s" s="2">
@@ -1156,108 +975,108 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" outlineLevel="3">
-      <c r="A17" t="s" s="5">
-        <v>6</v>
+    <row r="17" outlineLevel="1">
+      <c r="A17" t="s" s="3">
+        <v>21</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" outlineLevel="3">
-      <c r="A18" t="s" s="5">
-        <v>6</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" outlineLevel="2">
+      <c r="A18" t="s" s="4">
+        <v>21</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" outlineLevel="3">
-      <c r="A19" t="s" s="5">
-        <v>6</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" outlineLevel="2">
+      <c r="A19" t="s" s="4">
+        <v>21</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" outlineLevel="3">
-      <c r="A20" t="s" s="5">
-        <v>6</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" outlineLevel="2">
+      <c r="A20" t="s" s="4">
+        <v>21</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" outlineLevel="3">
-      <c r="A21" t="s" s="5">
-        <v>6</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" outlineLevel="2">
+      <c r="A21" t="s" s="4">
+        <v>21</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" outlineLevel="3">
-      <c r="A22" t="s" s="5">
-        <v>6</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" outlineLevel="2">
+      <c r="A22" t="s" s="4">
+        <v>21</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" outlineLevel="3">
-      <c r="A23" t="s" s="5">
-        <v>6</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" outlineLevel="2">
+      <c r="A23" t="s" s="4">
+        <v>21</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" outlineLevel="3">
-      <c r="A24" t="s" s="5">
-        <v>6</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" outlineLevel="2">
+      <c r="A24" t="s" s="4">
+        <v>21</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" outlineLevel="1">
-      <c r="A25" t="s" s="3">
         <v>29</v>
       </c>
+    </row>
+    <row r="25" outlineLevel="2">
+      <c r="A25" t="s" s="4">
+        <v>21</v>
+      </c>
       <c r="B25" t="s" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" outlineLevel="2">
       <c r="A26" t="s" s="4">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>7</v>
@@ -1266,53 +1085,53 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" outlineLevel="1">
-      <c r="A27" t="s" s="3">
+    <row r="27" outlineLevel="2">
+      <c r="A27" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>4</v>
       </c>
     </row>
     <row r="28" outlineLevel="2">
       <c r="A28" t="s" s="4">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
         <v>33</v>
       </c>
+    </row>
+    <row r="29" outlineLevel="2">
+      <c r="A29" t="s" s="4">
+        <v>21</v>
+      </c>
       <c r="B29" t="s" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" outlineLevel="1">
-      <c r="A30" t="s" s="3">
         <v>34</v>
       </c>
+    </row>
+    <row r="30" outlineLevel="2">
+      <c r="A30" t="s" s="4">
+        <v>21</v>
+      </c>
       <c r="B30" t="s" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" outlineLevel="2">
       <c r="A31" t="s" s="4">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>7</v>
@@ -1321,1450 +1140,1450 @@
         <v>36</v>
       </c>
     </row>
-    <row r="32" outlineLevel="1">
-      <c r="A32" t="s" s="3">
+    <row r="32" outlineLevel="2">
+      <c r="A32" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>4</v>
       </c>
     </row>
     <row r="33" outlineLevel="2">
       <c r="A33" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="34" outlineLevel="2">
       <c r="A34" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" outlineLevel="2">
       <c r="A35" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" outlineLevel="2">
       <c r="A36" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" outlineLevel="2">
       <c r="A37" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" outlineLevel="2">
       <c r="A38" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" outlineLevel="2">
       <c r="A39" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" outlineLevel="2">
       <c r="A40" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" outlineLevel="2">
       <c r="A41" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" outlineLevel="2">
       <c r="A42" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" outlineLevel="2">
       <c r="A43" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" outlineLevel="2">
       <c r="A44" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" outlineLevel="2">
       <c r="A45" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C45" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" outlineLevel="2">
+      <c r="A46" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>51</v>
-      </c>
-    </row>
-    <row r="46" outlineLevel="1">
-      <c r="A46" t="s" s="3">
-        <v>52</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>53</v>
       </c>
     </row>
     <row r="47" outlineLevel="2">
       <c r="A47" t="s" s="4">
+        <v>21</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="48" outlineLevel="2">
       <c r="A48" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" outlineLevel="2">
       <c r="A49" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" outlineLevel="2">
       <c r="A50" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" outlineLevel="2">
       <c r="A51" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" outlineLevel="2">
       <c r="A52" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" outlineLevel="2">
       <c r="A53" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" outlineLevel="2">
       <c r="A54" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" outlineLevel="2">
       <c r="A55" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" outlineLevel="2">
       <c r="A56" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" outlineLevel="2">
       <c r="A57" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" outlineLevel="2">
       <c r="A58" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" outlineLevel="2">
       <c r="A59" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>66</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" outlineLevel="2">
       <c r="A60" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>67</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" outlineLevel="2">
       <c r="A61" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" outlineLevel="2">
       <c r="A62" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>69</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" outlineLevel="2">
       <c r="A63" t="s" s="4">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="64" outlineLevel="2">
-      <c r="A64" t="s" s="4">
-        <v>52</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" outlineLevel="1">
+      <c r="A64" t="s" s="3">
+        <v>64</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>71</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" outlineLevel="2">
       <c r="A65" t="s" s="4">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" outlineLevel="2">
       <c r="A66" t="s" s="4">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="67" outlineLevel="2">
-      <c r="A67" t="s" s="4">
-        <v>52</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" outlineLevel="1">
+      <c r="A67" t="s" s="3">
+        <v>67</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" outlineLevel="2">
       <c r="A68" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" outlineLevel="2">
       <c r="A69" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" outlineLevel="2">
       <c r="A70" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71" outlineLevel="2">
       <c r="A71" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="72" outlineLevel="2">
       <c r="A72" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73" outlineLevel="2">
       <c r="A73" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" outlineLevel="2">
       <c r="A74" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" outlineLevel="2">
       <c r="A75" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="76" outlineLevel="2">
       <c r="A76" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="77" outlineLevel="2">
       <c r="A77" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78" outlineLevel="2">
       <c r="A78" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79" outlineLevel="2">
       <c r="A79" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" outlineLevel="2">
       <c r="A80" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81" outlineLevel="2">
       <c r="A81" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" outlineLevel="2">
       <c r="A82" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="83" outlineLevel="2">
       <c r="A83" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84" outlineLevel="2">
       <c r="A84" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" outlineLevel="2">
       <c r="A85" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86" outlineLevel="2">
       <c r="A86" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="87" outlineLevel="2">
       <c r="A87" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" outlineLevel="2">
       <c r="A88" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>53</v>
+        <v>89</v>
       </c>
     </row>
     <row r="89" outlineLevel="2">
       <c r="A89" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>54</v>
+        <v>90</v>
       </c>
     </row>
     <row r="90" outlineLevel="2">
       <c r="A90" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>55</v>
+        <v>91</v>
       </c>
     </row>
     <row r="91" outlineLevel="2">
       <c r="A91" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>56</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92" outlineLevel="2">
       <c r="A92" t="s" s="4">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="93" outlineLevel="1">
-      <c r="A93" t="s" s="3">
-        <v>95</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" outlineLevel="2">
+      <c r="A93" t="s" s="4">
+        <v>67</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>4</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" outlineLevel="2">
       <c r="A94" t="s" s="4">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" outlineLevel="2">
       <c r="A95" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C95" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="B95" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C95" t="s" s="2">
+    </row>
+    <row r="96" outlineLevel="2">
+      <c r="A96" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C96" t="s" s="2">
         <v>97</v>
-      </c>
-    </row>
-    <row r="96" outlineLevel="1">
-      <c r="A96" t="s" s="3">
-        <v>98</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>99</v>
       </c>
     </row>
     <row r="97" outlineLevel="2">
       <c r="A97" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C97" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="98" outlineLevel="2">
       <c r="A98" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="99" outlineLevel="2">
       <c r="A99" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" outlineLevel="2">
       <c r="A100" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" outlineLevel="2">
       <c r="A101" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="102" outlineLevel="2">
       <c r="A102" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" outlineLevel="2">
       <c r="A103" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" outlineLevel="2">
       <c r="A104" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="105" outlineLevel="2">
       <c r="A105" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106" outlineLevel="2">
       <c r="A106" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" outlineLevel="2">
       <c r="A107" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="108" outlineLevel="2">
       <c r="A108" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="109" outlineLevel="2">
       <c r="A109" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="110" outlineLevel="2">
       <c r="A110" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="111" outlineLevel="2">
       <c r="A111" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="112" outlineLevel="2">
       <c r="A112" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="113" outlineLevel="2">
       <c r="A113" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" outlineLevel="2">
       <c r="A114" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="115" outlineLevel="2">
       <c r="A115" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" outlineLevel="2">
       <c r="A116" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117" outlineLevel="2">
       <c r="A117" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118" outlineLevel="2">
       <c r="A118" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" outlineLevel="2">
       <c r="A119" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120" outlineLevel="2">
       <c r="A120" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="121" outlineLevel="2">
       <c r="A121" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="122" outlineLevel="2">
       <c r="A122" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="123" outlineLevel="2">
       <c r="A123" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="124" outlineLevel="2">
       <c r="A124" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" outlineLevel="2">
       <c r="A125" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="126" outlineLevel="2">
       <c r="A126" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="127" outlineLevel="2">
       <c r="A127" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="128" outlineLevel="2">
       <c r="A128" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="129" outlineLevel="2">
       <c r="A129" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="130" outlineLevel="2">
       <c r="A130" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="131" outlineLevel="2">
       <c r="A131" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="132" outlineLevel="2">
       <c r="A132" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="133" outlineLevel="2">
       <c r="A133" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="134" outlineLevel="2">
       <c r="A134" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="135" outlineLevel="2">
       <c r="A135" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="136" outlineLevel="2">
       <c r="A136" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="137" outlineLevel="2">
       <c r="A137" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="138" outlineLevel="2">
       <c r="A138" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="139" outlineLevel="2">
       <c r="A139" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="140" outlineLevel="2">
       <c r="A140" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="141" outlineLevel="2">
       <c r="A141" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="142" outlineLevel="2">
       <c r="A142" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="143" outlineLevel="2">
       <c r="A143" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="144" outlineLevel="2">
       <c r="A144" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="145" outlineLevel="2">
       <c r="A145" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="146" outlineLevel="2">
       <c r="A146" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="147" outlineLevel="2">
       <c r="A147" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="148" outlineLevel="2">
       <c r="A148" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="149" outlineLevel="2">
       <c r="A149" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="150" outlineLevel="2">
       <c r="A150" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="151" outlineLevel="2">
       <c r="A151" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="152" outlineLevel="2">
       <c r="A152" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="153" outlineLevel="2">
       <c r="A153" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154" outlineLevel="2">
       <c r="A154" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="155" outlineLevel="2">
       <c r="A155" t="s" s="4">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C155" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C156" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" outlineLevel="1">
+      <c r="A157" t="s" s="3">
         <v>158</v>
       </c>
-    </row>
-    <row r="156" outlineLevel="2">
-      <c r="A156" t="s" s="4">
-        <v>98</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C156" t="s" s="2">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="157" outlineLevel="2">
-      <c r="A157" t="s" s="4">
-        <v>98</v>
-      </c>
       <c r="B157" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>160</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" outlineLevel="2">
       <c r="A158" t="s" s="4">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C158" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="159" outlineLevel="1">
+      <c r="A159" t="s" s="3">
         <v>161</v>
       </c>
-    </row>
-    <row r="159" outlineLevel="2">
-      <c r="A159" t="s" s="4">
-        <v>98</v>
-      </c>
       <c r="B159" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>162</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" outlineLevel="2">
       <c r="A160" t="s" s="4">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C160" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" outlineLevel="3">
+      <c r="A161" t="s" s="5">
         <v>163</v>
       </c>
-    </row>
-    <row r="161" outlineLevel="2">
-      <c r="A161" t="s" s="4">
-        <v>98</v>
-      </c>
       <c r="B161" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C161" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" outlineLevel="4">
+      <c r="A162" t="s" s="6">
         <v>164</v>
       </c>
-    </row>
-    <row r="162" outlineLevel="2">
-      <c r="A162" t="s" s="4">
-        <v>98</v>
-      </c>
       <c r="B162" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C162" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" outlineLevel="5">
+      <c r="A163" t="s" s="7">
         <v>165</v>
-      </c>
-    </row>
-    <row r="163" outlineLevel="2">
-      <c r="A163" t="s" s="4">
-        <v>98</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>7</v>
@@ -2773,906 +2592,213 @@
         <v>166</v>
       </c>
     </row>
-    <row r="164" outlineLevel="2">
-      <c r="A164" t="s" s="4">
-        <v>98</v>
+    <row r="164" outlineLevel="3">
+      <c r="A164" t="s" s="5">
+        <v>167</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="165" outlineLevel="2">
-      <c r="A165" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" outlineLevel="4">
+      <c r="A165" t="s" s="6">
+        <v>168</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="166" outlineLevel="2">
-      <c r="A166" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" outlineLevel="5">
+      <c r="A166" t="s" s="7">
+        <v>169</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="167" outlineLevel="2">
-      <c r="A167" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" outlineLevel="6">
+      <c r="A167" t="s" s="8">
+        <v>170</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="168" outlineLevel="2">
-      <c r="A168" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" outlineLevel="7">
+      <c r="A168" t="s" s="9">
+        <v>171</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="169" outlineLevel="2">
-      <c r="A169" t="s" s="4">
-        <v>98</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="169" outlineLevel="1">
+      <c r="A169" t="s" s="3">
+        <v>173</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>172</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" outlineLevel="2">
       <c r="A170" t="s" s="4">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="171" outlineLevel="2">
-      <c r="A171" t="s" s="4">
-        <v>98</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="171" outlineLevel="1">
+      <c r="A171" t="s" s="3">
+        <v>176</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>174</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" outlineLevel="2">
       <c r="A172" t="s" s="4">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="173" outlineLevel="2">
-      <c r="A173" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" outlineLevel="3">
+      <c r="A173" t="s" s="5">
+        <v>177</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="174" outlineLevel="2">
-      <c r="A174" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" outlineLevel="4">
+      <c r="A174" t="s" s="6">
+        <v>178</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="175" outlineLevel="2">
-      <c r="A175" t="s" s="4">
-        <v>98</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="175" outlineLevel="3">
+      <c r="A175" t="s" s="5">
+        <v>163</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="176" outlineLevel="2">
-      <c r="A176" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" outlineLevel="4">
+      <c r="A176" t="s" s="6">
+        <v>164</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="177" outlineLevel="2">
-      <c r="A177" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" outlineLevel="5">
+      <c r="A177" t="s" s="7">
+        <v>165</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="178" outlineLevel="2">
-      <c r="A178" t="s" s="4">
-        <v>98</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="178" outlineLevel="3">
+      <c r="A178" t="s" s="5">
+        <v>167</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="179" outlineLevel="2">
-      <c r="A179" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" outlineLevel="4">
+      <c r="A179" t="s" s="6">
+        <v>168</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="180" outlineLevel="2">
-      <c r="A180" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" outlineLevel="5">
+      <c r="A180" t="s" s="7">
+        <v>169</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="181" outlineLevel="2">
-      <c r="A181" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" outlineLevel="6">
+      <c r="A181" t="s" s="8">
+        <v>170</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="182" outlineLevel="2">
-      <c r="A182" t="s" s="4">
-        <v>98</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" outlineLevel="7">
+      <c r="A182" t="s" s="9">
+        <v>171</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="183" outlineLevel="2">
-      <c r="A183" t="s" s="4">
-        <v>98</v>
-      </c>
-      <c r="B183" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C183" t="s" s="2">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="184" outlineLevel="2">
-      <c r="A184" t="s" s="4">
-        <v>98</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C184" t="s" s="2">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C185" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="186" outlineLevel="1">
-      <c r="A186" t="s" s="3">
-        <v>189</v>
-      </c>
-      <c r="B186" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C186" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="187" outlineLevel="2">
-      <c r="A187" t="s" s="4">
-        <v>190</v>
-      </c>
-      <c r="B187" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C187" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188" outlineLevel="3">
-      <c r="A188" t="s" s="5">
-        <v>191</v>
-      </c>
-      <c r="B188" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C188" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="189" outlineLevel="4">
-      <c r="A189" t="s" s="6">
-        <v>192</v>
-      </c>
-      <c r="B189" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C189" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="190" outlineLevel="5">
-      <c r="A190" t="s" s="7">
-        <v>193</v>
-      </c>
-      <c r="B190" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="191" outlineLevel="3">
-      <c r="A191" t="s" s="5">
-        <v>195</v>
-      </c>
-      <c r="B191" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C191" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="192" outlineLevel="4">
-      <c r="A192" t="s" s="6">
-        <v>196</v>
-      </c>
-      <c r="B192" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C192" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="193" outlineLevel="5">
-      <c r="A193" t="s" s="7">
-        <v>197</v>
-      </c>
-      <c r="B193" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C193" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="194" outlineLevel="6">
-      <c r="A194" t="s" s="8">
-        <v>198</v>
-      </c>
-      <c r="B194" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C194" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="195" outlineLevel="7">
-      <c r="A195" t="s" s="9">
-        <v>199</v>
-      </c>
-      <c r="B195" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C195" t="s" s="2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="196" outlineLevel="8">
-      <c r="A196" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B196" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C196" t="s" s="2">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="197" outlineLevel="8">
-      <c r="A197" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B197" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="198" outlineLevel="8">
-      <c r="A198" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B198" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C198" t="s" s="2">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="199" outlineLevel="8">
-      <c r="A199" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B199" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C199" t="s" s="2">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="200" outlineLevel="8">
-      <c r="A200" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B200" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C200" t="s" s="2">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="201" outlineLevel="8">
-      <c r="A201" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B201" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C201" t="s" s="2">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="202" outlineLevel="8">
-      <c r="A202" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B202" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C202" t="s" s="2">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="203" outlineLevel="8">
-      <c r="A203" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B203" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C203" t="s" s="2">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="204" outlineLevel="8">
-      <c r="A204" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B204" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C204" t="s" s="2">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="205" outlineLevel="8">
-      <c r="A205" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B205" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C205" t="s" s="2">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="206" outlineLevel="8">
-      <c r="A206" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B206" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C206" t="s" s="2">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="207" outlineLevel="8">
-      <c r="A207" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B207" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C207" t="s" s="2">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="208" outlineLevel="8">
-      <c r="A208" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B208" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C208" t="s" s="2">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="209" outlineLevel="8">
-      <c r="A209" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B209" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C209" t="s" s="2">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="210" outlineLevel="8">
-      <c r="A210" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B210" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C210" t="s" s="2">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="211" outlineLevel="8">
-      <c r="A211" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B211" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C211" t="s" s="2">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="212" outlineLevel="8">
-      <c r="A212" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B212" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C212" t="s" s="2">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="213" outlineLevel="8">
-      <c r="A213" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B213" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C213" t="s" s="2">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="214" outlineLevel="8">
-      <c r="A214" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B214" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C214" t="s" s="2">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="215" outlineLevel="1">
-      <c r="A215" t="s" s="3">
-        <v>220</v>
-      </c>
-      <c r="B215" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C215" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" outlineLevel="2">
-      <c r="A216" t="s" s="4">
-        <v>190</v>
-      </c>
-      <c r="B216" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C216" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" outlineLevel="3">
-      <c r="A217" t="s" s="5">
-        <v>221</v>
-      </c>
-      <c r="B217" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C217" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" outlineLevel="4">
-      <c r="A218" t="s" s="6">
-        <v>222</v>
-      </c>
-      <c r="B218" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C218" t="s" s="2">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="219" outlineLevel="3">
-      <c r="A219" t="s" s="5">
-        <v>191</v>
-      </c>
-      <c r="B219" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C219" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="220" outlineLevel="4">
-      <c r="A220" t="s" s="6">
-        <v>192</v>
-      </c>
-      <c r="B220" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C220" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" outlineLevel="5">
-      <c r="A221" t="s" s="7">
-        <v>193</v>
-      </c>
-      <c r="B221" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C221" t="s" s="2">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="222" outlineLevel="3">
-      <c r="A222" t="s" s="5">
-        <v>195</v>
-      </c>
-      <c r="B222" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C222" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" outlineLevel="4">
-      <c r="A223" t="s" s="6">
-        <v>196</v>
-      </c>
-      <c r="B223" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C223" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="224" outlineLevel="5">
-      <c r="A224" t="s" s="7">
-        <v>197</v>
-      </c>
-      <c r="B224" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C224" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="225" outlineLevel="6">
-      <c r="A225" t="s" s="8">
-        <v>198</v>
-      </c>
-      <c r="B225" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C225" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" outlineLevel="7">
-      <c r="A226" t="s" s="9">
-        <v>199</v>
-      </c>
-      <c r="B226" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C226" t="s" s="2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="227" outlineLevel="8">
-      <c r="A227" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B227" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C227" t="s" s="2">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="228" outlineLevel="8">
-      <c r="A228" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B228" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C228" t="s" s="2">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="229" outlineLevel="8">
-      <c r="A229" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B229" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C229" t="s" s="2">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="230" outlineLevel="8">
-      <c r="A230" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B230" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C230" t="s" s="2">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="231" outlineLevel="8">
-      <c r="A231" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B231" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C231" t="s" s="2">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="232" outlineLevel="8">
-      <c r="A232" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B232" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C232" t="s" s="2">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="233" outlineLevel="8">
-      <c r="A233" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B233" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C233" t="s" s="2">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="234" outlineLevel="8">
-      <c r="A234" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B234" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C234" t="s" s="2">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="235" outlineLevel="8">
-      <c r="A235" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B235" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C235" t="s" s="2">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="236" outlineLevel="8">
-      <c r="A236" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B236" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C236" t="s" s="2">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="237" outlineLevel="8">
-      <c r="A237" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C237" t="s" s="2">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="238" outlineLevel="8">
-      <c r="A238" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B238" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C238" t="s" s="2">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="239" outlineLevel="8">
-      <c r="A239" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B239" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C239" t="s" s="2">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="240" outlineLevel="8">
-      <c r="A240" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B240" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C240" t="s" s="2">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="241" outlineLevel="8">
-      <c r="A241" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C241" t="s" s="2">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="242" outlineLevel="8">
-      <c r="A242" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C242" t="s" s="2">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="243" outlineLevel="8">
-      <c r="A243" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C243" t="s" s="2">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="244" outlineLevel="8">
-      <c r="A244" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C244" t="s" s="2">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="245" outlineLevel="8">
-      <c r="A245" t="s" s="10">
-        <v>199</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C245" t="s" s="2">
-        <v>219</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/log/Table.xlsx
+++ b/log/Table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="188">
   <si>
     <t>Name</t>
   </si>
@@ -23,19 +23,41 @@
     <t>Details</t>
   </si>
   <si>
+    <t>Vivado Commands</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">refresh_hw_device -update_hw_probes false [lindex [get_hw_devices xc7a35t_0] 0]
+</t>
+  </si>
+  <si>
+    <t>Labtools 27-3361</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The debug hub core was not detected.
+Resolution: 
+1. Make sure the clock connected to the debug hub (dbg_hub) core is a free running clock and is active.
+2. Make sure the BSCAN_SWITCH_USER_MASK device property in Vivado Hardware Manager reflects the user scan chain setting in the design and refresh the device.  To determine the user scan chain setting in the design, open the implemented design and use 'get_property C_USER_SCAN_CHAIN [get_debug_cores dbg_hub]'.
+For more details on setting the scan chain property, consult the Vivado Debug and Programming User Guide (UG908).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refresh_hw_device [lindex [get_hw_devices xc7a35t_0] 0]
+</t>
+  </si>
+  <si>
     <t>Synthesis</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>D:\comp_sci\CS202 Computer Organization\OrganProj\cpu-project-team\src\debug_code\DebugController.v</t>
   </si>
   <si>
     <t>Synth 8-5788</t>
-  </si>
-  <si>
-    <t>Warning</t>
   </si>
   <si>
     <t xml:space="preserve">Register payload_reg[0] in module DebugController is has both Set and reset with same priority. This may cause simulation mismatches. Consider rewriting code 
@@ -689,6 +711,16 @@
   <si>
     <t xml:space="preserve">Router estimated timing not met.
 Resolution: For a complete and accurate timing signoff, report_timing_summary must be run after route_design. Alternatively, route_design can be run with the -timing_summary option to enable a complete timing signoff at the end of route_design.
+</t>
+  </si>
+  <si>
+    <t>Timing 38-282</t>
+  </si>
+  <si>
+    <t>Critical Warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The design failed to meet the timing requirements. Please see the timing summary report for details on the timing violations.
 </t>
   </si>
   <si>
@@ -843,15 +875,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" outlineLevel="2">
-      <c r="A5" t="s" s="4">
-        <v>6</v>
+    <row r="5" outlineLevel="1">
+      <c r="A5" t="s" s="3">
+        <v>9</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" outlineLevel="2">
@@ -862,34 +894,34 @@
         <v>7</v>
       </c>
       <c r="C6" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" outlineLevel="2">
-      <c r="A7" t="s" s="4">
-        <v>6</v>
-      </c>
       <c r="B7" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1">
+      <c r="A8" t="s" s="3">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" outlineLevel="2">
-      <c r="A8" t="s" s="4">
-        <v>6</v>
-      </c>
       <c r="B8" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" outlineLevel="2">
       <c r="A9" t="s" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>7</v>
@@ -900,7 +932,7 @@
     </row>
     <row r="10" outlineLevel="2">
       <c r="A10" t="s" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>7</v>
@@ -911,7 +943,7 @@
     </row>
     <row r="11" outlineLevel="2">
       <c r="A11" t="s" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>7</v>
@@ -922,7 +954,7 @@
     </row>
     <row r="12" outlineLevel="2">
       <c r="A12" t="s" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>7</v>
@@ -933,7 +965,7 @@
     </row>
     <row r="13" outlineLevel="2">
       <c r="A13" t="s" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>7</v>
@@ -944,7 +976,7 @@
     </row>
     <row r="14" outlineLevel="2">
       <c r="A14" t="s" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>7</v>
@@ -955,7 +987,7 @@
     </row>
     <row r="15" outlineLevel="2">
       <c r="A15" t="s" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>7</v>
@@ -966,7 +998,7 @@
     </row>
     <row r="16" outlineLevel="2">
       <c r="A16" t="s" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>7</v>
@@ -975,64 +1007,64 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" outlineLevel="1">
-      <c r="A17" t="s" s="3">
+    <row r="17" outlineLevel="2">
+      <c r="A17" t="s" s="4">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>21</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>22</v>
       </c>
     </row>
     <row r="18" outlineLevel="2">
       <c r="A18" t="s" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" outlineLevel="2">
       <c r="A19" t="s" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" outlineLevel="2">
       <c r="A20" t="s" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" outlineLevel="2">
       <c r="A21" t="s" s="4">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" outlineLevel="2">
-      <c r="A22" t="s" s="4">
-        <v>21</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1">
+      <c r="A22" t="s" s="3">
+        <v>26</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>7</v>
@@ -1043,7 +1075,7 @@
     </row>
     <row r="23" outlineLevel="2">
       <c r="A23" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>7</v>
@@ -1054,7 +1086,7 @@
     </row>
     <row r="24" outlineLevel="2">
       <c r="A24" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>7</v>
@@ -1065,7 +1097,7 @@
     </row>
     <row r="25" outlineLevel="2">
       <c r="A25" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>7</v>
@@ -1076,7 +1108,7 @@
     </row>
     <row r="26" outlineLevel="2">
       <c r="A26" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>7</v>
@@ -1087,7 +1119,7 @@
     </row>
     <row r="27" outlineLevel="2">
       <c r="A27" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>7</v>
@@ -1098,7 +1130,7 @@
     </row>
     <row r="28" outlineLevel="2">
       <c r="A28" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>7</v>
@@ -1109,7 +1141,7 @@
     </row>
     <row r="29" outlineLevel="2">
       <c r="A29" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>7</v>
@@ -1120,7 +1152,7 @@
     </row>
     <row r="30" outlineLevel="2">
       <c r="A30" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>7</v>
@@ -1131,7 +1163,7 @@
     </row>
     <row r="31" outlineLevel="2">
       <c r="A31" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>7</v>
@@ -1142,7 +1174,7 @@
     </row>
     <row r="32" outlineLevel="2">
       <c r="A32" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>7</v>
@@ -1153,7 +1185,7 @@
     </row>
     <row r="33" outlineLevel="2">
       <c r="A33" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>7</v>
@@ -1164,7 +1196,7 @@
     </row>
     <row r="34" outlineLevel="2">
       <c r="A34" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>7</v>
@@ -1175,7 +1207,7 @@
     </row>
     <row r="35" outlineLevel="2">
       <c r="A35" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>7</v>
@@ -1186,7 +1218,7 @@
     </row>
     <row r="36" outlineLevel="2">
       <c r="A36" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>7</v>
@@ -1197,7 +1229,7 @@
     </row>
     <row r="37" outlineLevel="2">
       <c r="A37" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>7</v>
@@ -1208,7 +1240,7 @@
     </row>
     <row r="38" outlineLevel="2">
       <c r="A38" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>7</v>
@@ -1219,7 +1251,7 @@
     </row>
     <row r="39" outlineLevel="2">
       <c r="A39" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>7</v>
@@ -1230,7 +1262,7 @@
     </row>
     <row r="40" outlineLevel="2">
       <c r="A40" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>7</v>
@@ -1241,7 +1273,7 @@
     </row>
     <row r="41" outlineLevel="2">
       <c r="A41" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>7</v>
@@ -1252,7 +1284,7 @@
     </row>
     <row r="42" outlineLevel="2">
       <c r="A42" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>7</v>
@@ -1263,7 +1295,7 @@
     </row>
     <row r="43" outlineLevel="2">
       <c r="A43" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>7</v>
@@ -1274,7 +1306,7 @@
     </row>
     <row r="44" outlineLevel="2">
       <c r="A44" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>7</v>
@@ -1285,7 +1317,7 @@
     </row>
     <row r="45" outlineLevel="2">
       <c r="A45" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>7</v>
@@ -1296,7 +1328,7 @@
     </row>
     <row r="46" outlineLevel="2">
       <c r="A46" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>7</v>
@@ -1307,7 +1339,7 @@
     </row>
     <row r="47" outlineLevel="2">
       <c r="A47" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>7</v>
@@ -1318,7 +1350,7 @@
     </row>
     <row r="48" outlineLevel="2">
       <c r="A48" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>7</v>
@@ -1329,7 +1361,7 @@
     </row>
     <row r="49" outlineLevel="2">
       <c r="A49" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>7</v>
@@ -1340,7 +1372,7 @@
     </row>
     <row r="50" outlineLevel="2">
       <c r="A50" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>7</v>
@@ -1351,7 +1383,7 @@
     </row>
     <row r="51" outlineLevel="2">
       <c r="A51" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>7</v>
@@ -1362,7 +1394,7 @@
     </row>
     <row r="52" outlineLevel="2">
       <c r="A52" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>7</v>
@@ -1373,7 +1405,7 @@
     </row>
     <row r="53" outlineLevel="2">
       <c r="A53" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>7</v>
@@ -1384,7 +1416,7 @@
     </row>
     <row r="54" outlineLevel="2">
       <c r="A54" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>7</v>
@@ -1395,7 +1427,7 @@
     </row>
     <row r="55" outlineLevel="2">
       <c r="A55" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>7</v>
@@ -1406,7 +1438,7 @@
     </row>
     <row r="56" outlineLevel="2">
       <c r="A56" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>7</v>
@@ -1417,7 +1449,7 @@
     </row>
     <row r="57" outlineLevel="2">
       <c r="A57" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>7</v>
@@ -1428,7 +1460,7 @@
     </row>
     <row r="58" outlineLevel="2">
       <c r="A58" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>7</v>
@@ -1439,128 +1471,128 @@
     </row>
     <row r="59" outlineLevel="2">
       <c r="A59" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" outlineLevel="2">
       <c r="A60" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" outlineLevel="2">
       <c r="A61" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>24</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" outlineLevel="2">
       <c r="A62" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>25</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" outlineLevel="2">
       <c r="A63" t="s" s="4">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" outlineLevel="1">
-      <c r="A64" t="s" s="3">
-        <v>64</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" outlineLevel="2">
+      <c r="A64" t="s" s="4">
+        <v>26</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" outlineLevel="2">
       <c r="A65" t="s" s="4">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" outlineLevel="2">
       <c r="A66" t="s" s="4">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="A67" t="s" s="3">
-        <v>67</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" outlineLevel="2">
+      <c r="A67" t="s" s="4">
+        <v>26</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>68</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" outlineLevel="2">
       <c r="A68" t="s" s="4">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C68" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1">
+      <c r="A69" t="s" s="3">
         <v>69</v>
       </c>
-    </row>
-    <row r="69" outlineLevel="2">
-      <c r="A69" t="s" s="4">
-        <v>67</v>
-      </c>
       <c r="B69" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>70</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" outlineLevel="2">
       <c r="A70" t="s" s="4">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>7</v>
@@ -1571,18 +1603,18 @@
     </row>
     <row r="71" outlineLevel="2">
       <c r="A71" t="s" s="4">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>7</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="72" outlineLevel="2">
-      <c r="A72" t="s" s="4">
-        <v>67</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1">
+      <c r="A72" t="s" s="3">
+        <v>72</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>7</v>
@@ -1593,7 +1625,7 @@
     </row>
     <row r="73" outlineLevel="2">
       <c r="A73" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>7</v>
@@ -1604,7 +1636,7 @@
     </row>
     <row r="74" outlineLevel="2">
       <c r="A74" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>7</v>
@@ -1615,7 +1647,7 @@
     </row>
     <row r="75" outlineLevel="2">
       <c r="A75" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>7</v>
@@ -1626,7 +1658,7 @@
     </row>
     <row r="76" outlineLevel="2">
       <c r="A76" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>7</v>
@@ -1637,7 +1669,7 @@
     </row>
     <row r="77" outlineLevel="2">
       <c r="A77" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>7</v>
@@ -1648,7 +1680,7 @@
     </row>
     <row r="78" outlineLevel="2">
       <c r="A78" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>7</v>
@@ -1659,7 +1691,7 @@
     </row>
     <row r="79" outlineLevel="2">
       <c r="A79" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>7</v>
@@ -1670,7 +1702,7 @@
     </row>
     <row r="80" outlineLevel="2">
       <c r="A80" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>7</v>
@@ -1681,7 +1713,7 @@
     </row>
     <row r="81" outlineLevel="2">
       <c r="A81" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>7</v>
@@ -1692,7 +1724,7 @@
     </row>
     <row r="82" outlineLevel="2">
       <c r="A82" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>7</v>
@@ -1703,7 +1735,7 @@
     </row>
     <row r="83" outlineLevel="2">
       <c r="A83" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>7</v>
@@ -1714,7 +1746,7 @@
     </row>
     <row r="84" outlineLevel="2">
       <c r="A84" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>7</v>
@@ -1725,7 +1757,7 @@
     </row>
     <row r="85" outlineLevel="2">
       <c r="A85" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>7</v>
@@ -1736,7 +1768,7 @@
     </row>
     <row r="86" outlineLevel="2">
       <c r="A86" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>7</v>
@@ -1747,7 +1779,7 @@
     </row>
     <row r="87" outlineLevel="2">
       <c r="A87" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>7</v>
@@ -1758,7 +1790,7 @@
     </row>
     <row r="88" outlineLevel="2">
       <c r="A88" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>7</v>
@@ -1769,7 +1801,7 @@
     </row>
     <row r="89" outlineLevel="2">
       <c r="A89" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>7</v>
@@ -1780,7 +1812,7 @@
     </row>
     <row r="90" outlineLevel="2">
       <c r="A90" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>7</v>
@@ -1791,7 +1823,7 @@
     </row>
     <row r="91" outlineLevel="2">
       <c r="A91" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>7</v>
@@ -1802,7 +1834,7 @@
     </row>
     <row r="92" outlineLevel="2">
       <c r="A92" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>7</v>
@@ -1813,7 +1845,7 @@
     </row>
     <row r="93" outlineLevel="2">
       <c r="A93" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>7</v>
@@ -1824,7 +1856,7 @@
     </row>
     <row r="94" outlineLevel="2">
       <c r="A94" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>7</v>
@@ -1835,7 +1867,7 @@
     </row>
     <row r="95" outlineLevel="2">
       <c r="A95" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>7</v>
@@ -1846,7 +1878,7 @@
     </row>
     <row r="96" outlineLevel="2">
       <c r="A96" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>7</v>
@@ -1857,7 +1889,7 @@
     </row>
     <row r="97" outlineLevel="2">
       <c r="A97" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>7</v>
@@ -1868,7 +1900,7 @@
     </row>
     <row r="98" outlineLevel="2">
       <c r="A98" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>7</v>
@@ -1879,7 +1911,7 @@
     </row>
     <row r="99" outlineLevel="2">
       <c r="A99" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>7</v>
@@ -1890,7 +1922,7 @@
     </row>
     <row r="100" outlineLevel="2">
       <c r="A100" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>7</v>
@@ -1901,7 +1933,7 @@
     </row>
     <row r="101" outlineLevel="2">
       <c r="A101" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>7</v>
@@ -1912,7 +1944,7 @@
     </row>
     <row r="102" outlineLevel="2">
       <c r="A102" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>7</v>
@@ -1923,7 +1955,7 @@
     </row>
     <row r="103" outlineLevel="2">
       <c r="A103" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>7</v>
@@ -1934,7 +1966,7 @@
     </row>
     <row r="104" outlineLevel="2">
       <c r="A104" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>7</v>
@@ -1945,7 +1977,7 @@
     </row>
     <row r="105" outlineLevel="2">
       <c r="A105" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>7</v>
@@ -1956,7 +1988,7 @@
     </row>
     <row r="106" outlineLevel="2">
       <c r="A106" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>7</v>
@@ -1967,7 +1999,7 @@
     </row>
     <row r="107" outlineLevel="2">
       <c r="A107" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>7</v>
@@ -1978,7 +2010,7 @@
     </row>
     <row r="108" outlineLevel="2">
       <c r="A108" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>7</v>
@@ -1989,7 +2021,7 @@
     </row>
     <row r="109" outlineLevel="2">
       <c r="A109" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>7</v>
@@ -2000,7 +2032,7 @@
     </row>
     <row r="110" outlineLevel="2">
       <c r="A110" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>7</v>
@@ -2011,7 +2043,7 @@
     </row>
     <row r="111" outlineLevel="2">
       <c r="A111" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>7</v>
@@ -2022,7 +2054,7 @@
     </row>
     <row r="112" outlineLevel="2">
       <c r="A112" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>7</v>
@@ -2033,7 +2065,7 @@
     </row>
     <row r="113" outlineLevel="2">
       <c r="A113" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>7</v>
@@ -2044,7 +2076,7 @@
     </row>
     <row r="114" outlineLevel="2">
       <c r="A114" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>7</v>
@@ -2055,7 +2087,7 @@
     </row>
     <row r="115" outlineLevel="2">
       <c r="A115" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>7</v>
@@ -2066,7 +2098,7 @@
     </row>
     <row r="116" outlineLevel="2">
       <c r="A116" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>7</v>
@@ -2077,7 +2109,7 @@
     </row>
     <row r="117" outlineLevel="2">
       <c r="A117" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>7</v>
@@ -2088,7 +2120,7 @@
     </row>
     <row r="118" outlineLevel="2">
       <c r="A118" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>7</v>
@@ -2099,7 +2131,7 @@
     </row>
     <row r="119" outlineLevel="2">
       <c r="A119" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>7</v>
@@ -2110,7 +2142,7 @@
     </row>
     <row r="120" outlineLevel="2">
       <c r="A120" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>7</v>
@@ -2121,7 +2153,7 @@
     </row>
     <row r="121" outlineLevel="2">
       <c r="A121" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>7</v>
@@ -2132,7 +2164,7 @@
     </row>
     <row r="122" outlineLevel="2">
       <c r="A122" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>7</v>
@@ -2143,7 +2175,7 @@
     </row>
     <row r="123" outlineLevel="2">
       <c r="A123" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>7</v>
@@ -2154,7 +2186,7 @@
     </row>
     <row r="124" outlineLevel="2">
       <c r="A124" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>7</v>
@@ -2165,7 +2197,7 @@
     </row>
     <row r="125" outlineLevel="2">
       <c r="A125" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>7</v>
@@ -2176,7 +2208,7 @@
     </row>
     <row r="126" outlineLevel="2">
       <c r="A126" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>7</v>
@@ -2187,7 +2219,7 @@
     </row>
     <row r="127" outlineLevel="2">
       <c r="A127" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>7</v>
@@ -2198,7 +2230,7 @@
     </row>
     <row r="128" outlineLevel="2">
       <c r="A128" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>7</v>
@@ -2209,7 +2241,7 @@
     </row>
     <row r="129" outlineLevel="2">
       <c r="A129" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>7</v>
@@ -2220,7 +2252,7 @@
     </row>
     <row r="130" outlineLevel="2">
       <c r="A130" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>7</v>
@@ -2231,7 +2263,7 @@
     </row>
     <row r="131" outlineLevel="2">
       <c r="A131" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>7</v>
@@ -2242,7 +2274,7 @@
     </row>
     <row r="132" outlineLevel="2">
       <c r="A132" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>7</v>
@@ -2253,7 +2285,7 @@
     </row>
     <row r="133" outlineLevel="2">
       <c r="A133" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>7</v>
@@ -2264,7 +2296,7 @@
     </row>
     <row r="134" outlineLevel="2">
       <c r="A134" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>7</v>
@@ -2275,7 +2307,7 @@
     </row>
     <row r="135" outlineLevel="2">
       <c r="A135" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>7</v>
@@ -2286,7 +2318,7 @@
     </row>
     <row r="136" outlineLevel="2">
       <c r="A136" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>7</v>
@@ -2297,7 +2329,7 @@
     </row>
     <row r="137" outlineLevel="2">
       <c r="A137" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>7</v>
@@ -2308,7 +2340,7 @@
     </row>
     <row r="138" outlineLevel="2">
       <c r="A138" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>7</v>
@@ -2319,7 +2351,7 @@
     </row>
     <row r="139" outlineLevel="2">
       <c r="A139" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>7</v>
@@ -2330,7 +2362,7 @@
     </row>
     <row r="140" outlineLevel="2">
       <c r="A140" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>7</v>
@@ -2341,7 +2373,7 @@
     </row>
     <row r="141" outlineLevel="2">
       <c r="A141" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>7</v>
@@ -2352,7 +2384,7 @@
     </row>
     <row r="142" outlineLevel="2">
       <c r="A142" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>7</v>
@@ -2363,7 +2395,7 @@
     </row>
     <row r="143" outlineLevel="2">
       <c r="A143" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>7</v>
@@ -2374,7 +2406,7 @@
     </row>
     <row r="144" outlineLevel="2">
       <c r="A144" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>7</v>
@@ -2385,7 +2417,7 @@
     </row>
     <row r="145" outlineLevel="2">
       <c r="A145" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>7</v>
@@ -2396,7 +2428,7 @@
     </row>
     <row r="146" outlineLevel="2">
       <c r="A146" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>7</v>
@@ -2407,7 +2439,7 @@
     </row>
     <row r="147" outlineLevel="2">
       <c r="A147" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>7</v>
@@ -2418,7 +2450,7 @@
     </row>
     <row r="148" outlineLevel="2">
       <c r="A148" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>7</v>
@@ -2429,7 +2461,7 @@
     </row>
     <row r="149" outlineLevel="2">
       <c r="A149" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>7</v>
@@ -2440,7 +2472,7 @@
     </row>
     <row r="150" outlineLevel="2">
       <c r="A150" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>7</v>
@@ -2451,7 +2483,7 @@
     </row>
     <row r="151" outlineLevel="2">
       <c r="A151" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>7</v>
@@ -2462,7 +2494,7 @@
     </row>
     <row r="152" outlineLevel="2">
       <c r="A152" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>7</v>
@@ -2473,7 +2505,7 @@
     </row>
     <row r="153" outlineLevel="2">
       <c r="A153" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>7</v>
@@ -2484,7 +2516,7 @@
     </row>
     <row r="154" outlineLevel="2">
       <c r="A154" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>7</v>
@@ -2495,7 +2527,7 @@
     </row>
     <row r="155" outlineLevel="2">
       <c r="A155" t="s" s="4">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>7</v>
@@ -2504,250 +2536,250 @@
         <v>156</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="s" s="2">
+    <row r="156" outlineLevel="2">
+      <c r="A156" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C156" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="B156" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C156" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="157" outlineLevel="1">
-      <c r="A157" t="s" s="3">
+    </row>
+    <row r="157" outlineLevel="2">
+      <c r="A157" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C157" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C157" t="s" s="2">
-        <v>4</v>
       </c>
     </row>
     <row r="158" outlineLevel="2">
       <c r="A158" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C158" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="B158" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C158" t="s" s="2">
+    </row>
+    <row r="159" outlineLevel="2">
+      <c r="A159" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C159" t="s" s="2">
         <v>160</v>
-      </c>
-    </row>
-    <row r="159" outlineLevel="1">
-      <c r="A159" t="s" s="3">
-        <v>161</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>4</v>
       </c>
     </row>
     <row r="160" outlineLevel="2">
       <c r="A160" t="s" s="4">
+        <v>72</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C160" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="B160" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C160" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="161" outlineLevel="3">
-      <c r="A161" t="s" s="5">
+      <c r="B161" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C161" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" outlineLevel="1">
+      <c r="A162" t="s" s="3">
         <v>163</v>
       </c>
-      <c r="B161" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C161" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="162" outlineLevel="4">
-      <c r="A162" t="s" s="6">
+      <c r="B162" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C162" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" outlineLevel="2">
+      <c r="A163" t="s" s="4">
         <v>164</v>
       </c>
-      <c r="B162" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="163" outlineLevel="5">
-      <c r="A163" t="s" s="7">
+      <c r="B163" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C163" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="B163" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C163" t="s" s="2">
+    </row>
+    <row r="164" outlineLevel="1">
+      <c r="A164" t="s" s="3">
         <v>166</v>
       </c>
-    </row>
-    <row r="164" outlineLevel="3">
-      <c r="A164" t="s" s="5">
+      <c r="B164" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" outlineLevel="2">
+      <c r="A165" t="s" s="4">
         <v>167</v>
       </c>
-      <c r="B164" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C164" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="165" outlineLevel="4">
-      <c r="A165" t="s" s="6">
+      <c r="B165" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C165" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" outlineLevel="3">
+      <c r="A166" t="s" s="5">
         <v>168</v>
       </c>
-      <c r="B165" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C165" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="166" outlineLevel="5">
-      <c r="A166" t="s" s="7">
+      <c r="B166" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" outlineLevel="4">
+      <c r="A167" t="s" s="6">
         <v>169</v>
       </c>
-      <c r="B166" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C166" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="167" outlineLevel="6">
-      <c r="A167" t="s" s="8">
+      <c r="B167" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" outlineLevel="5">
+      <c r="A168" t="s" s="7">
         <v>170</v>
       </c>
-      <c r="B167" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C167" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="168" outlineLevel="7">
-      <c r="A168" t="s" s="9">
+      <c r="B168" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C168" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="B168" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C168" t="s" s="2">
+    </row>
+    <row r="169" outlineLevel="3">
+      <c r="A169" t="s" s="5">
         <v>172</v>
       </c>
-    </row>
-    <row r="169" outlineLevel="1">
-      <c r="A169" t="s" s="3">
+      <c r="B169" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C169" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" outlineLevel="4">
+      <c r="A170" t="s" s="6">
         <v>173</v>
       </c>
-      <c r="B169" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="170" outlineLevel="2">
-      <c r="A170" t="s" s="4">
+      <c r="B170" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C170" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" outlineLevel="5">
+      <c r="A171" t="s" s="7">
         <v>174</v>
       </c>
-      <c r="B170" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C170" t="s" s="2">
+      <c r="B171" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C171" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" outlineLevel="6">
+      <c r="A172" t="s" s="8">
         <v>175</v>
       </c>
-    </row>
-    <row r="171" outlineLevel="1">
-      <c r="A171" t="s" s="3">
+      <c r="B172" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C172" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" outlineLevel="7">
+      <c r="A173" t="s" s="9">
         <v>176</v>
       </c>
-      <c r="B171" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C171" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="172" outlineLevel="2">
-      <c r="A172" t="s" s="4">
-        <v>162</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C172" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="173" outlineLevel="3">
-      <c r="A173" t="s" s="5">
+      <c r="B173" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C173" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="B173" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C173" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="174" outlineLevel="4">
-      <c r="A174" t="s" s="6">
+    </row>
+    <row r="174" outlineLevel="1">
+      <c r="A174" t="s" s="3">
         <v>178</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C174" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" outlineLevel="2">
+      <c r="A175" t="s" s="4">
         <v>179</v>
       </c>
-    </row>
-    <row r="175" outlineLevel="3">
-      <c r="A175" t="s" s="5">
-        <v>163</v>
-      </c>
       <c r="B175" t="s" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="176" outlineLevel="4">
-      <c r="A176" t="s" s="6">
-        <v>164</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="176" outlineLevel="2">
+      <c r="A176" t="s" s="4">
+        <v>181</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>4</v>
+        <v>182</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="177" outlineLevel="5">
-      <c r="A177" t="s" s="7">
-        <v>165</v>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="177" outlineLevel="1">
+      <c r="A177" t="s" s="3">
+        <v>184</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="178" outlineLevel="3">
-      <c r="A178" t="s" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" outlineLevel="2">
+      <c r="A178" t="s" s="4">
         <v>167</v>
       </c>
       <c r="B178" t="s" s="2">
@@ -2757,48 +2789,114 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" outlineLevel="4">
-      <c r="A179" t="s" s="6">
+    <row r="179" outlineLevel="3">
+      <c r="A179" t="s" s="5">
+        <v>185</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" outlineLevel="4">
+      <c r="A180" t="s" s="6">
+        <v>186</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C180" t="s" s="2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="181" outlineLevel="3">
+      <c r="A181" t="s" s="5">
         <v>168</v>
       </c>
-      <c r="B179" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="180" outlineLevel="5">
-      <c r="A180" t="s" s="7">
+      <c r="B181" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C181" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" outlineLevel="4">
+      <c r="A182" t="s" s="6">
         <v>169</v>
       </c>
-      <c r="B180" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C180" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="181" outlineLevel="6">
-      <c r="A181" t="s" s="8">
+      <c r="B182" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C182" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" outlineLevel="5">
+      <c r="A183" t="s" s="7">
         <v>170</v>
       </c>
-      <c r="B181" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="C181" t="s" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="182" outlineLevel="7">
-      <c r="A182" t="s" s="9">
+      <c r="B183" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C183" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="B182" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="C182" t="s" s="2">
+    </row>
+    <row r="184" outlineLevel="3">
+      <c r="A184" t="s" s="5">
         <v>172</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" outlineLevel="4">
+      <c r="A185" t="s" s="6">
+        <v>173</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C185" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" outlineLevel="5">
+      <c r="A186" t="s" s="7">
+        <v>174</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C186" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" outlineLevel="6">
+      <c r="A187" t="s" s="8">
+        <v>175</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" outlineLevel="7">
+      <c r="A188" t="s" s="9">
+        <v>176</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="C188" t="s" s="2">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
